--- a/output/reports/cv_experiment_KNN_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_qcut_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.635835886001587</v>
+        <v>2.354344606399536</v>
       </c>
       <c r="E2" t="n">
         <v>0.9962548380768484</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.671211957931519</v>
+        <v>2.570496082305908</v>
       </c>
       <c r="E3" t="n">
         <v>0.9970077248654106</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.043547630310059</v>
+        <v>2.916466474533081</v>
       </c>
       <c r="E4" t="n">
         <v>0.9973717366034205</v>
@@ -596,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>3.063344240188599</v>
+        <v>3.253458976745605</v>
       </c>
       <c r="E5" t="n">
         <v>0.9974269041414209</v>
@@ -692,7 +692,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.635835886001587</v>
+        <v>2.354344606399536</v>
       </c>
       <c r="E2" t="n">
         <v>0.9962548380768484</v>
@@ -727,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.671211957931519</v>
+        <v>2.570496082305908</v>
       </c>
       <c r="E3" t="n">
         <v>0.9970077248654106</v>
@@ -762,7 +762,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>3.043547630310059</v>
+        <v>2.916466474533081</v>
       </c>
       <c r="E4" t="n">
         <v>0.9973717366034205</v>
@@ -797,7 +797,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>3.063344240188599</v>
+        <v>3.253458976745605</v>
       </c>
       <c r="E5" t="n">
         <v>0.9974269041414209</v>

--- a/output/reports/cv_experiment_KNN_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.354344606399536</v>
+        <v>0.211597204208374</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.570496082305908</v>
+        <v>0.100106954574585</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.916466474533081</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9973717366034205</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.253458976745605</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9974269041414209</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.354344606399536</v>
+        <v>0.211597204208374</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.570496082305908</v>
+        <v>0.100106954574585</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.916466474533081</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9973717366034205</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.253458976745605</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9974269041414209</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'uniform', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
